--- a/NOC_EndUser_CSAT.xlsx
+++ b/NOC_EndUser_CSAT.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30431"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30611"/>
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chilutej\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="36" documentId="13_ncr:1_{92230CBE-44A0-4D69-AEB0-3C6623379592}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A70C2642-3991-4552-B80E-3D3046C3BC43}"/>
+  <xr:revisionPtr revIDLastSave="63" documentId="13_ncr:1_{92230CBE-44A0-4D69-AEB0-3C6623379592}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{428F2309-4BCE-4AEC-A204-55FCD98DFBF5}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CSAT Dump" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1131" uniqueCount="557">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1237" uniqueCount="612">
   <si>
     <t>Number</t>
   </si>
@@ -1711,6 +1711,171 @@
   </si>
   <si>
     <t>INC9438448</t>
+  </si>
+  <si>
+    <t>INC10339748</t>
+  </si>
+  <si>
+    <t>Leo Chen</t>
+  </si>
+  <si>
+    <t>INC10321634</t>
+  </si>
+  <si>
+    <t>Warinah .</t>
+  </si>
+  <si>
+    <t>INC10338185</t>
+  </si>
+  <si>
+    <t>Jose Luis Velasco</t>
+  </si>
+  <si>
+    <t>INC10335786</t>
+  </si>
+  <si>
+    <t>INC10330241</t>
+  </si>
+  <si>
+    <t>Daniel Downs</t>
+  </si>
+  <si>
+    <t>INC10325774</t>
+  </si>
+  <si>
+    <t>Dacian Domocos</t>
+  </si>
+  <si>
+    <t>INC10326090</t>
+  </si>
+  <si>
+    <t>Barbara Hentschke</t>
+  </si>
+  <si>
+    <t>INC10318405</t>
+  </si>
+  <si>
+    <t>Harshita Soni</t>
+  </si>
+  <si>
+    <t>INC10315020</t>
+  </si>
+  <si>
+    <t>INC10299021</t>
+  </si>
+  <si>
+    <t>Hady Abdelbaki</t>
+  </si>
+  <si>
+    <t>INC10300402</t>
+  </si>
+  <si>
+    <t>Ignasi Ortiz</t>
+  </si>
+  <si>
+    <t>INC10296940</t>
+  </si>
+  <si>
+    <t>Zafruddin Mohammed</t>
+  </si>
+  <si>
+    <t>INC10300665</t>
+  </si>
+  <si>
+    <t>David Motorca</t>
+  </si>
+  <si>
+    <t>INC10296597</t>
+  </si>
+  <si>
+    <t>INC10293798</t>
+  </si>
+  <si>
+    <t>SG206 - Shop - Changi City point FO ccp.asin@adidas.com</t>
+  </si>
+  <si>
+    <t>INC10298005</t>
+  </si>
+  <si>
+    <t>INC10292344</t>
+  </si>
+  <si>
+    <t>Gianfranco Risaliti</t>
+  </si>
+  <si>
+    <t>INC10288051</t>
+  </si>
+  <si>
+    <t>INC10282432</t>
+  </si>
+  <si>
+    <t>INC10285278</t>
+  </si>
+  <si>
+    <t>INC10277841</t>
+  </si>
+  <si>
+    <t>INC10253635</t>
+  </si>
+  <si>
+    <t>Jonas Echtner</t>
+  </si>
+  <si>
+    <t>INC10282216</t>
+  </si>
+  <si>
+    <t>INC10277859</t>
+  </si>
+  <si>
+    <t>INC10275343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4978_DE_adidas_FOES_Wertheim </t>
+  </si>
+  <si>
+    <t>INC10234179</t>
+  </si>
+  <si>
+    <t>Burhan Ahmed</t>
+  </si>
+  <si>
+    <t>INC10274565</t>
+  </si>
+  <si>
+    <t>Bryce Kho</t>
+  </si>
+  <si>
+    <t>INC10274527</t>
+  </si>
+  <si>
+    <t>INC10271977</t>
+  </si>
+  <si>
+    <t>INC10274662</t>
+  </si>
+  <si>
+    <t>INC10274618</t>
+  </si>
+  <si>
+    <t>INC10222416</t>
+  </si>
+  <si>
+    <t>Andrey Kardamanov</t>
+  </si>
+  <si>
+    <t>INC10270795</t>
+  </si>
+  <si>
+    <t>INC10244545</t>
+  </si>
+  <si>
+    <t>Yukiko Baba</t>
+  </si>
+  <si>
+    <t>INC10264635</t>
+  </si>
+  <si>
+    <t>Overall Rating</t>
   </si>
 </sst>
 </file>
@@ -1720,7 +1885,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -1756,6 +1921,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -1784,7 +1955,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1806,6 +1977,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="22" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2142,7 +2325,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D375"/>
+  <dimension ref="A1:D410"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="17.7109375" style="2" customWidth="1"/>
@@ -7401,6 +7584,496 @@
         <v>45</v>
       </c>
     </row>
+    <row r="376" spans="1:4" ht="15" customHeight="1">
+      <c r="A376" s="10" t="s">
+        <v>557</v>
+      </c>
+      <c r="B376" s="11">
+        <v>46295.461377314816</v>
+      </c>
+      <c r="C376" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D376" s="10" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="377" spans="1:4" ht="15" customHeight="1">
+      <c r="A377" s="10" t="s">
+        <v>559</v>
+      </c>
+      <c r="B377" s="11">
+        <v>46295.500775462962</v>
+      </c>
+      <c r="C377" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D377" s="10" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="378" spans="1:4" ht="15" customHeight="1">
+      <c r="A378" s="10" t="s">
+        <v>561</v>
+      </c>
+      <c r="B378" s="11">
+        <v>46294.751585648148</v>
+      </c>
+      <c r="C378" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D378" s="10" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="379" spans="1:4" ht="15" customHeight="1">
+      <c r="A379" s="10" t="s">
+        <v>563</v>
+      </c>
+      <c r="B379" s="11">
+        <v>46294.394884259258</v>
+      </c>
+      <c r="C379" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D379" s="10" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="380" spans="1:4" ht="15" customHeight="1">
+      <c r="A380" s="10" t="s">
+        <v>564</v>
+      </c>
+      <c r="B380" s="11">
+        <v>46290.897291666668</v>
+      </c>
+      <c r="C380" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D380" s="10" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="381" spans="1:4" ht="15" customHeight="1">
+      <c r="A381" s="10" t="s">
+        <v>566</v>
+      </c>
+      <c r="B381" s="11">
+        <v>46289.576504629629</v>
+      </c>
+      <c r="C381" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D381" s="10" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="382" spans="1:4" ht="15" customHeight="1">
+      <c r="A382" s="10" t="s">
+        <v>568</v>
+      </c>
+      <c r="B382" s="11">
+        <v>46289.639884259261</v>
+      </c>
+      <c r="C382" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D382" s="10" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="383" spans="1:4" ht="15" customHeight="1">
+      <c r="A383" s="10" t="s">
+        <v>570</v>
+      </c>
+      <c r="B383" s="11">
+        <v>46287.442766203705</v>
+      </c>
+      <c r="C383" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D383" s="10" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="384" spans="1:4" ht="15" customHeight="1">
+      <c r="A384" s="10" t="s">
+        <v>572</v>
+      </c>
+      <c r="B384" s="11">
+        <v>46286.386597222219</v>
+      </c>
+      <c r="C384" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D384" s="10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="385" spans="1:4" ht="15" customHeight="1">
+      <c r="A385" s="10" t="s">
+        <v>573</v>
+      </c>
+      <c r="B385" s="11">
+        <v>46283.544583333336</v>
+      </c>
+      <c r="C385" s="10" t="s">
+        <v>451</v>
+      </c>
+      <c r="D385" s="10" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="386" spans="1:4" ht="15" customHeight="1">
+      <c r="A386" s="10" t="s">
+        <v>575</v>
+      </c>
+      <c r="B386" s="11">
+        <v>46281.467175925929</v>
+      </c>
+      <c r="C386" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D386" s="10" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="387" spans="1:4" ht="15" customHeight="1">
+      <c r="A387" s="10" t="s">
+        <v>577</v>
+      </c>
+      <c r="B387" s="11">
+        <v>46281.265370370369</v>
+      </c>
+      <c r="C387" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D387" s="10" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="388" spans="1:4" ht="15" customHeight="1">
+      <c r="A388" s="10" t="s">
+        <v>579</v>
+      </c>
+      <c r="B388" s="11">
+        <v>46280.919386574074</v>
+      </c>
+      <c r="C388" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D388" s="10" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="389" spans="1:4" ht="15" customHeight="1">
+      <c r="A389" s="10" t="s">
+        <v>581</v>
+      </c>
+      <c r="B389" s="11">
+        <v>46280.493425925924</v>
+      </c>
+      <c r="C389" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D389" s="10" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="390" spans="1:4" ht="15" customHeight="1">
+      <c r="A390" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="B390" s="11">
+        <v>46280.383333333331</v>
+      </c>
+      <c r="C390" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D390" s="10" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="391" spans="1:4" ht="15" customHeight="1">
+      <c r="A391" s="10" t="s">
+        <v>584</v>
+      </c>
+      <c r="B391" s="11">
+        <v>46279.444120370368</v>
+      </c>
+      <c r="C391" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D391" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="392" spans="1:4" ht="15" customHeight="1">
+      <c r="A392" s="10" t="s">
+        <v>585</v>
+      </c>
+      <c r="B392" s="11">
+        <v>46276.42627314815</v>
+      </c>
+      <c r="C392" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D392" s="10" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="393" spans="1:4" ht="15" customHeight="1">
+      <c r="A393" s="10" t="s">
+        <v>587</v>
+      </c>
+      <c r="B393" s="11">
+        <v>46275.235335648147</v>
+      </c>
+      <c r="C393" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D393" s="10" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="394" spans="1:4" ht="15" customHeight="1">
+      <c r="A394" s="10" t="s">
+        <v>588</v>
+      </c>
+      <c r="B394" s="11">
+        <v>46274.391377314816</v>
+      </c>
+      <c r="C394" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D394" s="10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="395" spans="1:4" ht="15" customHeight="1">
+      <c r="A395" s="10" t="s">
+        <v>589</v>
+      </c>
+      <c r="B395" s="11">
+        <v>46274.343217592592</v>
+      </c>
+      <c r="C395" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D395" s="10" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="396" spans="1:4" ht="15" customHeight="1">
+      <c r="A396" s="10" t="s">
+        <v>590</v>
+      </c>
+      <c r="B396" s="11">
+        <v>46273.095567129632</v>
+      </c>
+      <c r="C396" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D396" s="10" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="397" spans="1:4" ht="15" customHeight="1">
+      <c r="A397" s="10" t="s">
+        <v>591</v>
+      </c>
+      <c r="B397" s="11">
+        <v>46273.488807870373</v>
+      </c>
+      <c r="C397" s="10" t="s">
+        <v>451</v>
+      </c>
+      <c r="D397" s="10" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="398" spans="1:4" ht="15" customHeight="1">
+      <c r="A398" s="10" t="s">
+        <v>593</v>
+      </c>
+      <c r="B398" s="11">
+        <v>46272.451666666668</v>
+      </c>
+      <c r="C398" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D398" s="10" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="399" spans="1:4" ht="15" customHeight="1">
+      <c r="A399" s="10" t="s">
+        <v>594</v>
+      </c>
+      <c r="B399" s="11">
+        <v>46272.365833333337</v>
+      </c>
+      <c r="C399" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D399" s="10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="400" spans="1:4" ht="15" customHeight="1">
+      <c r="A400" s="10" t="s">
+        <v>595</v>
+      </c>
+      <c r="B400" s="11">
+        <v>46270.550729166665</v>
+      </c>
+      <c r="C400" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D400" s="10" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="401" spans="1:4" ht="15" customHeight="1">
+      <c r="A401" s="10" t="s">
+        <v>597</v>
+      </c>
+      <c r="B401" s="11">
+        <v>46269.488553240742</v>
+      </c>
+      <c r="C401" s="10" t="s">
+        <v>451</v>
+      </c>
+      <c r="D401" s="10" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="402" spans="1:4" ht="15" customHeight="1">
+      <c r="A402" s="10" t="s">
+        <v>599</v>
+      </c>
+      <c r="B402" s="11">
+        <v>46269.214386574073</v>
+      </c>
+      <c r="C402" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D402" s="10" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="403" spans="1:4" ht="15" customHeight="1">
+      <c r="A403" s="10" t="s">
+        <v>601</v>
+      </c>
+      <c r="B403" s="11">
+        <v>46268.259618055556</v>
+      </c>
+      <c r="C403" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D403" s="10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="404" spans="1:4" ht="15" customHeight="1">
+      <c r="A404" s="10" t="s">
+        <v>602</v>
+      </c>
+      <c r="B404" s="11">
+        <v>46268.326064814813</v>
+      </c>
+      <c r="C404" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D404" s="10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="405" spans="1:4" ht="15" customHeight="1">
+      <c r="A405" s="10" t="s">
+        <v>603</v>
+      </c>
+      <c r="B405" s="11">
+        <v>46268.260381944441</v>
+      </c>
+      <c r="C405" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D405" s="10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="406" spans="1:4" ht="15" customHeight="1">
+      <c r="A406" s="10" t="s">
+        <v>604</v>
+      </c>
+      <c r="B406" s="11">
+        <v>46268.217141203706</v>
+      </c>
+      <c r="C406" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D406" s="10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="407" spans="1:4" ht="15" customHeight="1">
+      <c r="A407" s="10" t="s">
+        <v>605</v>
+      </c>
+      <c r="B407" s="11">
+        <v>46267.196030092593</v>
+      </c>
+      <c r="C407" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D407" s="10" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="408" spans="1:4" ht="15" customHeight="1">
+      <c r="A408" s="10" t="s">
+        <v>607</v>
+      </c>
+      <c r="B408" s="11">
+        <v>46266.972175925926</v>
+      </c>
+      <c r="C408" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D408" s="10" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="409" spans="1:4" ht="15" customHeight="1">
+      <c r="A409" s="10" t="s">
+        <v>608</v>
+      </c>
+      <c r="B409" s="11">
+        <v>46266.446863425925</v>
+      </c>
+      <c r="C409" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D409" s="10" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="410" spans="1:4" ht="15" customHeight="1">
+      <c r="A410" s="10" t="s">
+        <v>610</v>
+      </c>
+      <c r="B410" s="11">
+        <v>46266.479467592595</v>
+      </c>
+      <c r="C410" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D410" s="10" t="s">
+        <v>162</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D375" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7410,7 +8083,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D3BBB97-36B2-4A6C-9269-968F87F0DA53}">
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="13.28515625" customWidth="1"/>
@@ -7419,9 +8092,10 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
     <col min="6" max="6" width="16.42578125" customWidth="1"/>
+    <col min="7" max="7" width="17.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="20.45" customHeight="1">
+    <row r="1" spans="1:7" ht="20.45" customHeight="1">
       <c r="A1" s="6"/>
       <c r="B1" s="6" t="s">
         <v>550</v>
@@ -7438,8 +8112,11 @@
       <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="G1" s="6" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="15">
       <c r="A2" s="5">
         <v>45839</v>
       </c>
@@ -7458,8 +8135,12 @@
       <c r="F2" s="7">
         <v>45</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
+      <c r="G2" s="9">
+        <f>SUM(E2:F2)/SUM(B2:F2)</f>
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="15">
       <c r="A3" s="5">
         <v>46235</v>
       </c>
@@ -7478,8 +8159,12 @@
       <c r="F3" s="7">
         <v>44</v>
       </c>
-    </row>
-    <row r="4" spans="1:6">
+      <c r="G3" s="9">
+        <f t="shared" ref="G3:G16" si="0">SUM(E3:F3)/SUM(B3:F3)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15">
       <c r="A4" s="5">
         <v>46266</v>
       </c>
@@ -7498,8 +8183,12 @@
       <c r="F4" s="7">
         <v>25</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
+      <c r="G4" s="9">
+        <f t="shared" si="0"/>
+        <v>0.88888888888888884</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15">
       <c r="A5" s="5">
         <v>45931</v>
       </c>
@@ -7518,8 +8207,12 @@
       <c r="F5" s="7">
         <v>46</v>
       </c>
-    </row>
-    <row r="6" spans="1:6">
+      <c r="G5" s="9">
+        <f t="shared" si="0"/>
+        <v>0.94915254237288138</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15">
       <c r="A6" s="5">
         <v>45962</v>
       </c>
@@ -7538,8 +8231,12 @@
       <c r="F6" s="7">
         <v>42</v>
       </c>
-    </row>
-    <row r="7" spans="1:6">
+      <c r="G6" s="9">
+        <f t="shared" si="0"/>
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15">
       <c r="A7" s="5">
         <v>45992</v>
       </c>
@@ -7558,8 +8255,12 @@
       <c r="F7" s="7">
         <v>27</v>
       </c>
-    </row>
-    <row r="8" spans="1:6">
+      <c r="G7" s="9">
+        <f t="shared" si="0"/>
+        <v>0.967741935483871</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15">
       <c r="A8" s="5">
         <v>46023</v>
       </c>
@@ -7578,8 +8279,12 @@
       <c r="F8" s="7">
         <v>25</v>
       </c>
-    </row>
-    <row r="9" spans="1:6">
+      <c r="G8" s="9">
+        <f t="shared" si="0"/>
+        <v>0.96551724137931039</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15">
       <c r="A9" s="5">
         <v>46054</v>
       </c>
@@ -7598,8 +8303,12 @@
       <c r="F9" s="7">
         <v>21</v>
       </c>
-    </row>
-    <row r="10" spans="1:6">
+      <c r="G9" s="9">
+        <f t="shared" si="0"/>
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="15">
       <c r="A10" s="5">
         <v>46082</v>
       </c>
@@ -7618,8 +8327,12 @@
       <c r="F10" s="7">
         <v>34</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" ht="15">
+      <c r="G10" s="9">
+        <f t="shared" si="0"/>
+        <v>0.94736842105263153</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="15">
       <c r="A11" s="5">
         <v>46113</v>
       </c>
@@ -7638,8 +8351,12 @@
       <c r="F11" s="7">
         <v>33</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" ht="15">
+      <c r="G11" s="9">
+        <f t="shared" si="0"/>
+        <v>0.91666666666666663</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="15">
       <c r="A12" s="5">
         <v>46143</v>
       </c>
@@ -7658,8 +8375,12 @@
       <c r="F12" s="7">
         <v>30</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" ht="15">
+      <c r="G12" s="9">
+        <f t="shared" si="0"/>
+        <v>0.94594594594594594</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="15">
       <c r="A13" s="5">
         <v>46174</v>
       </c>
@@ -7678,8 +8399,12 @@
       <c r="F13" s="7">
         <v>28</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" ht="15">
+      <c r="G13" s="9">
+        <f t="shared" si="0"/>
+        <v>0.97058823529411764</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="15">
       <c r="A14" s="5">
         <v>46204</v>
       </c>
@@ -7698,8 +8423,12 @@
       <c r="F14" s="7">
         <v>30</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" ht="15">
+      <c r="G14" s="9">
+        <f t="shared" si="0"/>
+        <v>0.94117647058823528</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="15">
       <c r="A15" s="5">
         <v>46235</v>
       </c>
@@ -7718,13 +8447,54 @@
       <c r="F15" s="7">
         <v>38</v>
       </c>
-    </row>
+      <c r="G15" s="9">
+        <f t="shared" si="0"/>
+        <v>0.93617021276595747</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="15">
+      <c r="A16" s="5">
+        <v>46266</v>
+      </c>
+      <c r="B16" s="8">
+        <v>0</v>
+      </c>
+      <c r="C16" s="8">
+        <v>0</v>
+      </c>
+      <c r="D16" s="8">
+        <v>0</v>
+      </c>
+      <c r="E16" s="8">
+        <v>3</v>
+      </c>
+      <c r="F16" s="8">
+        <v>32</v>
+      </c>
+      <c r="G16" s="9">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" ht="15"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Whatfor_x003f_ xmlns="2ee2d9e9-b7c3-4f8e-9687-c946c1044a73" xsi:nil="true"/>
+    <TaxCatchAll xmlns="dc4dcb21-90d3-4695-adc8-464bc3ea11a9" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2ee2d9e9-b7c3-4f8e-9687-c946c1044a73">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010071D348EA6C2F134F8CCD7A14FAB5DA39" ma:contentTypeVersion="20" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a0a68d9dfe8c1d188178482050519e57">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="2ee2d9e9-b7c3-4f8e-9687-c946c1044a73" xmlns:ns3="dc4dcb21-90d3-4695-adc8-464bc3ea11a9" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d6a210401e4afca4fde04e1ac7d5fad7" ns2:_="" ns3:_="">
     <xsd:import namespace="2ee2d9e9-b7c3-4f8e-9687-c946c1044a73"/>
@@ -7993,7 +8763,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -8002,28 +8772,16 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Whatfor_x003f_ xmlns="2ee2d9e9-b7c3-4f8e-9687-c946c1044a73" xsi:nil="true"/>
-    <TaxCatchAll xmlns="dc4dcb21-90d3-4695-adc8-464bc3ea11a9" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2ee2d9e9-b7c3-4f8e-9687-c946c1044a73">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3D65E716-B97F-49A8-8EE7-289850D1C55D}"/>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{671E1ABD-9AC8-4F52-93B8-C0B88BEBB60D}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2B2E03D1-ABD0-4C7C-B8C1-A3E9EEC6759C}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3D65E716-B97F-49A8-8EE7-289850D1C55D}"/>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
